--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N96_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N96_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.64652529318499</v>
+        <v>3.03006036014256</v>
       </c>
       <c r="D2" t="n">
-        <v>19.0430157062354</v>
+        <v>3.094490052263253</v>
       </c>
       <c r="E2" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F2" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.44214790333085</v>
+        <v>5.596849034291263</v>
       </c>
       <c r="D3" t="n">
-        <v>7.551790262105744</v>
+        <v>1.227165917592183</v>
       </c>
       <c r="E3" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F3" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.1075137904953</v>
+        <v>3.917470990955486</v>
       </c>
       <c r="D4" t="n">
-        <v>23.27457641147166</v>
+        <v>3.782118666864144</v>
       </c>
       <c r="E4" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F4" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.99186418799136</v>
+        <v>7.636177930548596</v>
       </c>
       <c r="D5" t="n">
-        <v>24.43737375824963</v>
+        <v>3.971073235715565</v>
       </c>
       <c r="E5" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F5" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.50249980485335</v>
+        <v>3.981656218288669</v>
       </c>
       <c r="D6" t="n">
-        <v>27.30823419361776</v>
+        <v>4.437588056462887</v>
       </c>
       <c r="E6" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F6" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.38509088135422</v>
+        <v>4.93757726822006</v>
       </c>
       <c r="D7" t="n">
-        <v>28.59331368153947</v>
+        <v>4.646413473250164</v>
       </c>
       <c r="E7" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F7" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.03529613405536</v>
+        <v>5.693235621783995</v>
       </c>
       <c r="D8" t="n">
-        <v>36.42495814981359</v>
+        <v>5.919055699344709</v>
       </c>
       <c r="E8" t="n">
-        <v>8.663467303427369</v>
+        <v>1.407813436806947</v>
       </c>
       <c r="F8" t="n">
-        <v>8.297921494921734</v>
+        <v>1.348412242924782</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
